--- a/pcb/esp32p4/mainboard/pcb assembly JLC/p2_pcb_esp32p4_v1_4_pos_JLC.xlsx
+++ b/pcb/esp32p4/mainboard/pcb assembly JLC/p2_pcb_esp32p4_v1_4_pos_JLC.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\Proj_i\picoheld2_hardware\picoheld2_public\picoheld2\pcb\esp32p4\mainboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\Proj_i\picoheld2_hardware\picoheld2_public\picoheld2\pcb\esp32p4\mainboard\pcb assembly JLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1461,7 +1461,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>82.340199999999996</v>
+        <v>82.420199999999994</v>
       </c>
       <c r="C24">
         <v>-127.4</v>
@@ -2198,7 +2198,7 @@
         <v>-117.19499999999999</v>
       </c>
       <c r="D67">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E67" t="s">
         <v>2</v>

--- a/pcb/esp32p4/mainboard/pcb assembly JLC/p2_pcb_esp32p4_v1_4_pos_JLC.xlsx
+++ b/pcb/esp32p4/mainboard/pcb assembly JLC/p2_pcb_esp32p4_v1_4_pos_JLC.xlsx
@@ -1376,10 +1376,10 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>126.7</v>
+        <v>125.5</v>
       </c>
       <c r="C19">
-        <v>-65.599999999999994</v>
+        <v>-65.099999999999994</v>
       </c>
       <c r="D19">
         <v>180</v>

--- a/pcb/esp32p4/mainboard/pcb assembly JLC/p2_pcb_esp32p4_v1_4_pos_JLC.xlsx
+++ b/pcb/esp32p4/mainboard/pcb assembly JLC/p2_pcb_esp32p4_v1_4_pos_JLC.xlsx
@@ -1478,13 +1478,13 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>99.1</v>
+        <v>102.3</v>
       </c>
       <c r="C25">
         <v>-89</v>
       </c>
       <c r="D25">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
         <v>2</v>
